--- a/AI_Inventory_Risk_Assessment_Workbook_SANITIZED.xlsx
+++ b/AI_Inventory_Risk_Assessment_Workbook_SANITIZED.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rdusa/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rdusa/work/crycos/AlignAICommunity/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD89A6C-FDF4-6343-91B6-F9F755EF2A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98AEB4A3-E5A1-9641-A773-EF7EDC2C3713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15080" yWindow="-21000" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1338" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1338" uniqueCount="596">
   <si>
     <t>AI RMF Profiles - Reference (P1-P20)</t>
   </si>
@@ -988,18 +988,9 @@
     <t>AI-003</t>
   </si>
   <si>
-    <t>CustomGPT.ai</t>
-  </si>
-  <si>
     <t>JMP Learnbot</t>
   </si>
   <si>
-    <t>AI used with JMP Learnbot</t>
-  </si>
-  <si>
-    <t>Limited group with access to Chemical compositions</t>
-  </si>
-  <si>
     <t>Data and questions provided by the user specific to the navigation of the JMP Pro tool</t>
   </si>
   <si>
@@ -1027,9 +1018,6 @@
     <t>All-in-one AI video platform to enhance training and communications; videos can be translated in 160+ languages</t>
   </si>
   <si>
-    <t>HR, Operations; Luis may also use for his videos</t>
-  </si>
-  <si>
     <t>Scripts and source material provided by the user; synthetic stock avatars and voices; generated video</t>
   </si>
   <si>
@@ -1060,9 +1048,6 @@
     <t>AI-006</t>
   </si>
   <si>
-    <t>Pictory.AI</t>
-  </si>
-  <si>
     <t>AI video generator for Company communications channels</t>
   </si>
   <si>
@@ -1081,12 +1066,6 @@
     <t>AI-007</t>
   </si>
   <si>
-    <t>Inside Hazard Navigator</t>
-  </si>
-  <si>
-    <t>To develop an AI tool used to query our EHS&amp;S risk assessment data, MOC, and other process safety data - PILOT DEVELOPMENT ONLY</t>
-  </si>
-  <si>
     <t>System Diagrams or Documentation; Operational Procedures</t>
   </si>
   <si>
@@ -1886,6 +1865,30 @@
   </si>
   <si>
     <t>Not applicable, data is from a single site.</t>
+  </si>
+  <si>
+    <t>HR, Operations; others may also use for his videos</t>
+  </si>
+  <si>
+    <t>To develop an AI tool used to query safety risk assessment data, MOC, and other process safety data - PILOT DEVELOPMENT ONLY</t>
+  </si>
+  <si>
+    <t>Potential Hazard Navigator</t>
+  </si>
+  <si>
+    <t>Startreck.AI</t>
+  </si>
+  <si>
+    <t>SomeGPT.ai</t>
+  </si>
+  <si>
+    <t>AI used with UI interface bot</t>
+  </si>
+  <si>
+    <t>Limited group with access to specific data</t>
+  </si>
+  <si>
+    <t>Data and questions provided by the user specific to the navigation of the UI Pro tool</t>
   </si>
 </sst>
 </file>
@@ -2030,24 +2033,24 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4230,7 +4233,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>175</v>
       </c>
       <c r="B1" s="10"/>
@@ -4243,7 +4246,7 @@
       <c r="I1" s="10"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="12" t="s">
         <v>176</v>
       </c>
       <c r="B2" s="10"/>
@@ -4270,17 +4273,17 @@
       <c r="H5" s="10"/>
     </row>
     <row r="6" spans="1:9" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="12">
+      <c r="A6" s="14">
         <f>COUNTA('AI Inventory'!$A$5:$A$11)</f>
         <v>7</v>
       </c>
       <c r="B6" s="10"/>
-      <c r="D6" s="12">
+      <c r="D6" s="14">
         <f>COUNTIF('AI Inventory'!$R$5:$R$11,"Approved")</f>
         <v>3</v>
       </c>
       <c r="E6" s="10"/>
-      <c r="G6" s="12">
+      <c r="G6" s="14">
         <f>COUNTIF('AI Inventory'!$R$5:$R$11,"Pending / Needs Documentation")</f>
         <v>2</v>
       </c>
@@ -4301,17 +4304,17 @@
       <c r="H8" s="10"/>
     </row>
     <row r="9" spans="1:9" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="12">
+      <c r="A9" s="14">
         <f>COUNTIF('AI Inventory'!$H$5:$H$11,"High")</f>
         <v>4</v>
       </c>
       <c r="B9" s="10"/>
-      <c r="D9" s="12">
+      <c r="D9" s="14">
         <f>COUNTIF('AI Inventory'!$H$5:$H$11,"Critical")</f>
         <v>0</v>
       </c>
       <c r="E9" s="10"/>
-      <c r="G9" s="12">
+      <c r="G9" s="14">
         <f>COUNTIF('AI Inventory'!$N$5:$N$11,"Yes")</f>
         <v>2</v>
       </c>
@@ -4332,17 +4335,17 @@
       <c r="H11" s="10"/>
     </row>
     <row r="12" spans="1:9" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="12">
+      <c r="A12" s="14">
         <f>COUNTIF('AI Inventory'!$L$5:$L$11,"Confidential")</f>
         <v>3</v>
       </c>
       <c r="B12" s="10"/>
-      <c r="D12" s="12">
+      <c r="D12" s="14">
         <f>COUNTIF('AI Inventory'!$L$5:$L$11,"Sensitive")</f>
         <v>0</v>
       </c>
       <c r="E12" s="10"/>
-      <c r="G12" s="12">
+      <c r="G12" s="14">
         <f>COUNTIF('AI Inventory'!$M$5:$M$11,"Yes")</f>
         <v>2</v>
       </c>
@@ -4363,17 +4366,17 @@
       <c r="H14" s="10"/>
     </row>
     <row r="15" spans="1:9" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="12">
+      <c r="A15" s="14">
         <f>COUNTIFS('AI Inventory'!$A$5:$A$11,"?*",'AI Inventory'!$T$5:$T$11,"P*")</f>
         <v>7</v>
       </c>
       <c r="B15" s="10"/>
-      <c r="D15" s="12">
+      <c r="D15" s="14">
         <f>COUNTIFS('AI Inventory'!$A$5:$A$11,"?*",'AI Inventory'!$T$5:$T$11,"")</f>
         <v>0</v>
       </c>
       <c r="E15" s="10"/>
-      <c r="G15" s="12">
+      <c r="G15" s="14">
         <f>SUMPRODUCT(--(COUNTIF('AI Inventory'!$T$5:$T$11,Profiles!$A$4:$A$23)&gt;0))</f>
         <v>5</v>
       </c>
@@ -4386,14 +4389,14 @@
       <c r="B17" s="10"/>
     </row>
     <row r="18" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="12">
+      <c r="A18" s="14">
         <f>COUNTIFS('Risk Assessment'!$A$4:$A$10,"?*",'Risk Assessment'!$F$4:$F$10,"High")+COUNTIFS('Risk Assessment'!$A$4:$A$10,"?*",'Risk Assessment'!$F$4:$F$10,"Critical")</f>
         <v>5</v>
       </c>
       <c r="B18" s="10"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="16" t="s">
         <v>190</v>
       </c>
       <c r="B21" s="10"/>
@@ -5212,10 +5215,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="G9:H9"/>
     <mergeCell ref="A34:I34"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="D9:E9"/>
@@ -5226,14 +5225,16 @@
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A21:H21"/>
     <mergeCell ref="G15:H15"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="G14:H14"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="D6:E6"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="G5:H5"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="G6:H6"/>
@@ -5242,6 +5243,8 @@
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="G8:H8"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="G14:H14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
@@ -5271,8 +5274,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
-        <v>483</v>
+      <c r="A1" s="9" t="s">
+        <v>476</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -5290,7 +5293,7 @@
       <c r="O1" s="10"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="11" t="s">
         <v>254</v>
       </c>
       <c r="B2" s="10"/>
@@ -5316,34 +5319,34 @@
         <v>257</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>486</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>493</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>266</v>
@@ -5352,7 +5355,7 @@
         <v>267</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -5388,14 +5391,14 @@
         <v>Approved</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="J4" s="2" t="str">
         <f>IFERROR(INDEX('AI Inventory'!$R$5:$R$11,MATCH(A4,'AI Inventory'!$A$5:$A$11,0)),"")</f>
         <v>Approved</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="L4" s="4" t="str">
         <f>IF('AI Inventory'!Q5="","",'AI Inventory'!Q5)</f>
@@ -5447,14 +5450,14 @@
         <v>Not Required</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="J5" s="2" t="str">
         <f>IFERROR(INDEX('AI Inventory'!$R$5:$R$11,MATCH(A5,'AI Inventory'!$A$5:$A$11,0)),"")</f>
         <v>Approved with Conditions</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="L5" s="4" t="str">
         <f>IF('AI Inventory'!Q6="","",'AI Inventory'!Q6)</f>
@@ -5506,14 +5509,14 @@
         <v>Not Required</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="J6" s="2" t="str">
         <f>IFERROR(INDEX('AI Inventory'!$R$5:$R$11,MATCH(A6,'AI Inventory'!$A$5:$A$11,0)),"")</f>
         <v>Approved</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="L6" s="4" t="str">
         <f>IF('AI Inventory'!Q7="","",'AI Inventory'!Q7)</f>
@@ -5542,7 +5545,7 @@
         <v>Synthesia</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="D7" s="2" t="str">
         <f>IFERROR(IF(INDEX('Vendor &amp; Security'!$D$4:$D$10,MATCH(A7,'Vendor &amp; Security'!$A$4:$A$10,0))="Rejected","Rejected",IF(INDEX('Vendor &amp; Security'!$D$4:$D$10,MATCH(A7,'Vendor &amp; Security'!$A$4:$A$10,0))="Approved","Approved",IF(INDEX('Vendor &amp; Security'!$D$4:$D$10,MATCH(A7,'Vendor &amp; Security'!$A$4:$A$10,0))="Approved with Conditions","Approved with Conditions","Pending"))),"")</f>
@@ -5565,14 +5568,14 @@
         <v>Not Required</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="J7" s="2" t="str">
         <f>IFERROR(INDEX('AI Inventory'!$R$5:$R$11,MATCH(A7,'AI Inventory'!$A$5:$A$11,0)),"")</f>
         <v>Pending / Needs Documentation</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="L7" s="4" t="str">
         <f>IF('AI Inventory'!Q8="","",'AI Inventory'!Q8)</f>
@@ -5601,7 +5604,7 @@
         <v>Levy AI</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="D8" s="2" t="str">
         <f>IFERROR(IF(INDEX('Vendor &amp; Security'!$D$4:$D$10,MATCH(A8,'Vendor &amp; Security'!$A$4:$A$10,0))="Rejected","Rejected",IF(INDEX('Vendor &amp; Security'!$D$4:$D$10,MATCH(A8,'Vendor &amp; Security'!$A$4:$A$10,0))="Approved","Approved",IF(INDEX('Vendor &amp; Security'!$D$4:$D$10,MATCH(A8,'Vendor &amp; Security'!$A$4:$A$10,0))="Approved with Conditions","Approved with Conditions","Pending"))),"")</f>
@@ -5624,14 +5627,14 @@
         <v>Not Submitted</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="J8" s="2" t="str">
         <f>IFERROR(INDEX('AI Inventory'!$R$5:$R$11,MATCH(A8,'AI Inventory'!$A$5:$A$11,0)),"")</f>
         <v>Pending / Needs Documentation</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="L8" s="4" t="str">
         <f>IF('AI Inventory'!Q9="","",'AI Inventory'!Q9)</f>
@@ -5657,7 +5660,7 @@
       </c>
       <c r="B9" s="2" t="str">
         <f>'AI Inventory'!C10</f>
-        <v>Pictory.AI</v>
+        <v>Startreck.AI</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>230</v>
@@ -5683,14 +5686,14 @@
         <v>Rejected</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="J9" s="2" t="str">
         <f>IFERROR(INDEX('AI Inventory'!$R$5:$R$11,MATCH(A9,'AI Inventory'!$A$5:$A$11,0)),"")</f>
         <v>Rejected</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="L9" s="4" t="str">
         <f>IF('AI Inventory'!Q10="","",'AI Inventory'!Q10)</f>
@@ -5716,7 +5719,7 @@
       </c>
       <c r="B10" s="2" t="str">
         <f>'AI Inventory'!C11</f>
-        <v>Inside Hazard Navigator</v>
+        <v>Potential Hazard Navigator</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>226</v>
@@ -5742,14 +5745,14 @@
         <v>Approved</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="J10" s="2" t="str">
         <f>IFERROR(INDEX('AI Inventory'!$R$5:$R$11,MATCH(A10,'AI Inventory'!$A$5:$A$11,0)),"")</f>
         <v>Approved</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="L10" s="4" t="str">
         <f>IF('AI Inventory'!Q11="","",'AI Inventory'!Q11)</f>
@@ -5820,8 +5823,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
-        <v>500</v>
+      <c r="A1" s="9" t="s">
+        <v>493</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -5848,49 +5851,49 @@
         <v>257</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>502</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>509</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -5915,19 +5918,19 @@
         <v>282</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>40</v>
@@ -5969,22 +5972,22 @@
         <v>282</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>40</v>
@@ -6026,28 +6029,28 @@
         <v>282</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>40</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="N6" s="4">
         <f t="shared" si="0"/>
@@ -6088,19 +6091,19 @@
         <v>282</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>40</v>
@@ -6145,19 +6148,19 @@
         <v>282</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>40</v>
@@ -6187,7 +6190,7 @@
       </c>
       <c r="B9" s="2" t="str">
         <f>'AI Inventory'!C10</f>
-        <v>Pictory.AI</v>
+        <v>Startreck.AI</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>282</v>
@@ -6202,22 +6205,22 @@
         <v>292</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="J9" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>518</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>525</v>
       </c>
       <c r="M9" s="2"/>
       <c r="N9" s="4" t="str">
@@ -6244,7 +6247,7 @@
       </c>
       <c r="B10" s="2" t="str">
         <f>'AI Inventory'!C11</f>
-        <v>Inside Hazard Navigator</v>
+        <v>Potential Hazard Navigator</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>282</v>
@@ -6259,25 +6262,25 @@
         <v>282</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>56</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="N10" s="4">
         <f t="shared" si="0"/>
@@ -6332,8 +6335,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
-        <v>529</v>
+      <c r="A1" s="9" t="s">
+        <v>522</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -6362,10 +6365,10 @@
         <v>225</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>11</v>
@@ -6380,25 +6383,25 @@
         <v>217</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="64" customHeight="1" x14ac:dyDescent="0.2">
@@ -6409,10 +6412,10 @@
         <v>213</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>282</v>
@@ -6430,25 +6433,25 @@
         <v>218</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>232</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="64" customHeight="1" x14ac:dyDescent="0.2">
@@ -6462,7 +6465,7 @@
         <v>227</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>292</v>
@@ -6474,31 +6477,31 @@
         <v>24</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>219</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>233</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>247</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="64" customHeight="1" x14ac:dyDescent="0.2">
@@ -6512,10 +6515,10 @@
         <v>228</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>56</v>
@@ -6524,31 +6527,31 @@
         <v>35</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>220</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>234</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>248</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="64" customHeight="1" x14ac:dyDescent="0.2">
@@ -6562,13 +6565,13 @@
         <v>226</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>42</v>
@@ -6577,25 +6580,25 @@
         <v>221</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>235</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>249</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -6603,7 +6606,7 @@
         <v>229</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>49</v>
@@ -6612,22 +6615,22 @@
         <v>222</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>236</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>250</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>226</v>
@@ -6644,16 +6647,16 @@
         <v>237</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>251</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>229</v>
@@ -6661,7 +6664,7 @@
     </row>
     <row r="10" spans="1:16" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C10" s="2" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>66</v>
@@ -6670,10 +6673,10 @@
         <v>238</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>230</v>
@@ -6687,10 +6690,10 @@
         <v>239</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -6701,10 +6704,10 @@
         <v>240</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -6715,10 +6718,10 @@
         <v>241</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -6729,10 +6732,10 @@
         <v>242</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -6743,10 +6746,10 @@
         <v>243</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -6757,10 +6760,10 @@
         <v>244</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
     </row>
     <row r="17" spans="7:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -6842,7 +6845,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>252</v>
       </c>
       <c r="B1" s="10"/>
@@ -6872,7 +6875,7 @@
       <c r="Z1" s="10"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="12" t="s">
         <v>253</v>
       </c>
       <c r="B2" s="10"/>
@@ -6902,7 +6905,7 @@
       <c r="Z2" s="10"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="11" t="s">
         <v>254</v>
       </c>
       <c r="B3" s="10"/>
@@ -7180,22 +7183,22 @@
         <v>294</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>296</v>
-      </c>
       <c r="D7" s="2" t="s">
-        <v>297</v>
+        <v>593</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>298</v>
+        <v>594</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>220</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>299</v>
+        <v>595</v>
       </c>
       <c r="H7" s="2" t="str">
         <f t="shared" si="0"/>
@@ -7210,7 +7213,7 @@
         <v>Matches profile</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>27</v>
@@ -7222,13 +7225,13 @@
         <v>292</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="R7" s="2" t="s">
         <v>226</v>
@@ -7256,7 +7259,7 @@
         <v>Annual</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="Z7" s="2" t="str">
         <f>IFERROR(INDEX('Risk Assessment'!$F$4:$F$10,MATCH(A7,'Risk Assessment'!$A$4:$A$10,0)),"")</f>
@@ -7265,25 +7268,25 @@
     </row>
     <row r="8" spans="1:26" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>308</v>
+        <v>588</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>218</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="H8" s="2" t="str">
         <f t="shared" si="0"/>
@@ -7310,10 +7313,10 @@
         <v>292</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="Q8" s="4"/>
       <c r="R8" s="2" t="s">
@@ -7342,7 +7345,7 @@
         <v>Semiannual; Quarterly if external-facing</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="Z8" s="2" t="str">
         <f>IFERROR(INDEX('Risk Assessment'!$F$4:$F$10,MATCH(A8,'Risk Assessment'!$A$4:$A$10,0)),"")</f>
@@ -7351,25 +7354,25 @@
     </row>
     <row r="9" spans="1:26" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>219</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H9" s="2" t="str">
         <f t="shared" si="0"/>
@@ -7396,10 +7399,10 @@
         <v>282</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="Q9" s="4"/>
       <c r="R9" s="2" t="s">
@@ -7428,7 +7431,7 @@
         <v>Quarterly</v>
       </c>
       <c r="Y9" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="Z9" s="2" t="str">
         <f>IFERROR(INDEX('Risk Assessment'!$F$4:$F$10,MATCH(A9,'Risk Assessment'!$A$4:$A$10,0)),"")</f>
@@ -7437,25 +7440,25 @@
     </row>
     <row r="10" spans="1:26" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>319</v>
+        <v>591</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>319</v>
+        <v>591</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>218</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="H10" s="2" t="str">
         <f t="shared" si="0"/>
@@ -7482,10 +7485,10 @@
         <v>292</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="Q10" s="4"/>
       <c r="R10" s="2" t="s">
@@ -7514,7 +7517,7 @@
         <v>Semiannual; Quarterly if external-facing</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="Z10" s="2" t="str">
         <f>IFERROR(INDEX('Risk Assessment'!$F$4:$F$10,MATCH(A10,'Risk Assessment'!$A$4:$A$10,0)),"")</f>
@@ -7523,25 +7526,25 @@
     </row>
     <row r="11" spans="1:26" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>326</v>
+        <v>590</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>327</v>
+        <v>589</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>221</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="H11" s="2" t="str">
         <f t="shared" si="0"/>
@@ -7568,13 +7571,13 @@
         <v>292</v>
       </c>
       <c r="O11" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q11" s="4" t="s">
         <v>323</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="Q11" s="4" t="s">
-        <v>330</v>
       </c>
       <c r="R11" s="2" t="s">
         <v>226</v>
@@ -7602,7 +7605,7 @@
         <v>At conclusion, or annually</v>
       </c>
       <c r="Y11" s="2" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="Z11" s="2" t="str">
         <f>IFERROR(INDEX('Risk Assessment'!$F$4:$F$10,MATCH(A11,'Risk Assessment'!$A$4:$A$10,0)),"")</f>
@@ -7678,7 +7681,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="10"/>
@@ -7693,7 +7696,7 @@
       <c r="K1" s="10"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="10"/>
@@ -8469,16 +8472,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
-        <v>332</v>
+      <c r="A1" s="9" t="s">
+        <v>325</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="9" t="s">
-        <v>333</v>
+      <c r="A2" s="12" t="s">
+        <v>326</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -8486,13 +8489,13 @@
     </row>
     <row r="3" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>191</v>
@@ -8503,10 +8506,10 @@
         <v>75</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>66</v>
@@ -8517,10 +8520,10 @@
         <v>174</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>167</v>
@@ -8531,10 +8534,10 @@
         <v>84</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>76</v>
@@ -8545,10 +8548,10 @@
         <v>57</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>49</v>
@@ -8559,10 +8562,10 @@
         <v>65</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>58</v>
@@ -8573,13 +8576,13 @@
         <v>92</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -8587,13 +8590,13 @@
         <v>48</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -8601,10 +8604,10 @@
         <v>159</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>149</v>
@@ -8615,10 +8618,10 @@
         <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>24</v>
@@ -8629,10 +8632,10 @@
         <v>23</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>13</v>
@@ -8643,10 +8646,10 @@
         <v>41</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>35</v>
@@ -8654,16 +8657,16 @@
     </row>
     <row r="15" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
     </row>
   </sheetData>
@@ -8707,8 +8710,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
-        <v>365</v>
+      <c r="A1" s="9" t="s">
+        <v>358</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -8730,7 +8733,7 @@
       <c r="S1" s="10"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A2" s="16"/>
+      <c r="A2" s="11"/>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
       <c r="D2" s="10"/>
@@ -8758,55 +8761,55 @@
         <v>257</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>215</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>270</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="144" customHeight="1" x14ac:dyDescent="0.2">
@@ -8845,10 +8848,10 @@
         <v>250</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="L4" s="2" t="str">
         <f t="shared" ref="L4:L10" si="1">IF(OR(D4="High",D4="Critical"),"Yes","No")</f>
@@ -8919,10 +8922,10 @@
         <v>247</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="L5" s="2" t="str">
         <f t="shared" si="1"/>
@@ -8993,10 +8996,10 @@
         <v>250</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="L6" s="2" t="str">
         <f t="shared" si="1"/>
@@ -9067,10 +9070,10 @@
         <v>249</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="L7" s="2" t="str">
         <f t="shared" si="1"/>
@@ -9141,10 +9144,10 @@
         <v>247</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="L8" s="2" t="str">
         <f t="shared" si="1"/>
@@ -9186,7 +9189,7 @@
       </c>
       <c r="B9" s="2" t="str">
         <f>INDEX('AI Inventory'!$C$5:$C$11,6)</f>
-        <v>Pictory.AI</v>
+        <v>Startreck.AI</v>
       </c>
       <c r="C9" s="2" t="str">
         <f>IFERROR(INDEX('AI Inventory'!$H$5:$H$11,MATCH(A9,'AI Inventory'!$A$5:$A$11,0)),"")</f>
@@ -9215,10 +9218,10 @@
         <v>249</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="L9" s="2" t="str">
         <f t="shared" si="1"/>
@@ -9260,7 +9263,7 @@
       </c>
       <c r="B10" s="2" t="str">
         <f>INDEX('AI Inventory'!$C$5:$C$11,7)</f>
-        <v>Inside Hazard Navigator</v>
+        <v>Potential Hazard Navigator</v>
       </c>
       <c r="C10" s="2" t="str">
         <f>IFERROR(INDEX('AI Inventory'!$H$5:$H$11,MATCH(A10,'AI Inventory'!$A$5:$A$11,0)),"")</f>
@@ -9289,10 +9292,10 @@
         <v>248</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="L10" s="2" t="str">
         <f t="shared" si="1"/>
@@ -9369,8 +9372,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
-        <v>389</v>
+      <c r="A1" s="9" t="s">
+        <v>382</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -9399,8 +9402,8 @@
       <c r="Z1" s="10"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A2" s="9" t="s">
-        <v>390</v>
+      <c r="A2" s="12" t="s">
+        <v>383</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -9429,7 +9432,7 @@
       <c r="Z2" s="10"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="11" t="s">
         <v>254</v>
       </c>
       <c r="B3" s="10"/>
@@ -9505,7 +9508,7 @@
         <v>244</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="Q4" s="1" t="s">
         <v>247</v>
@@ -9526,16 +9529,16 @@
         <v>274</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="96" customHeight="1" x14ac:dyDescent="0.2">
@@ -9605,7 +9608,7 @@
         <v>282</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="W5" s="2" t="str">
         <f t="shared" ref="W5:W11" si="0">_xlfn.TEXTJOIN(", ",TRUE,IF(C5="Yes","Data leakage and disclosure",""),IF(D5="Yes","Prompt injection and adversarial input",""),IF(E5="Yes","Hallucination and incorrect output",""),IF(F5="Yes","Unauthorized data retention",""),IF(G5="Yes","Model drift and degradation",""),IF(H5="Yes","Data poisoning",""),IF(I5="Yes","Model theft or extraction",""),IF(J5="Yes","Overreliance and automation bias",""),IF(K5="Yes","Bias and harmful output",""),IF(L5="Yes","Third-party and value chain risk",""),IF(M5="Yes","Information security risk",""),IF(N5="Yes","Privacy risk",""),IF(O5="Yes","Regulatory and legal risk",""))</f>
@@ -9691,7 +9694,7 @@
         <v>282</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="W6" s="2" t="str">
         <f t="shared" si="0"/>
@@ -9777,7 +9780,7 @@
         <v>282</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="W7" s="2" t="str">
         <f t="shared" si="0"/>
@@ -9863,7 +9866,7 @@
         <v>282</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="W8" s="2" t="str">
         <f t="shared" si="0"/>
@@ -9949,7 +9952,7 @@
         <v>282</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="W9" s="2" t="str">
         <f t="shared" si="0"/>
@@ -9975,7 +9978,7 @@
       </c>
       <c r="B10" s="2" t="str">
         <f>INDEX('AI Inventory'!$C$5:$C$11,6)</f>
-        <v>Pictory.AI</v>
+        <v>Startreck.AI</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>282</v>
@@ -10035,7 +10038,7 @@
         <v>282</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="W10" s="2" t="str">
         <f t="shared" si="0"/>
@@ -10061,7 +10064,7 @@
       </c>
       <c r="B11" s="2" t="str">
         <f>INDEX('AI Inventory'!$C$5:$C$11,7)</f>
-        <v>Inside Hazard Navigator</v>
+        <v>Potential Hazard Navigator</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>282</v>
@@ -10121,7 +10124,7 @@
         <v>282</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="W11" s="2" t="str">
         <f t="shared" si="0"/>
@@ -10184,8 +10187,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
-        <v>399</v>
+      <c r="A1" s="9" t="s">
+        <v>392</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -10210,7 +10213,7 @@
       <c r="V1" s="10"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="11" t="s">
         <v>254</v>
       </c>
       <c r="B2" s="10"/>
@@ -10243,13 +10246,13 @@
         <v>257</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>223</v>
@@ -10270,37 +10273,37 @@
         <v>265</v>
       </c>
       <c r="L3" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="S3" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="T3" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="V3" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="4" spans="1:22" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -10313,7 +10316,7 @@
         <v>Copilot</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="D4" s="2" t="str">
         <f t="shared" ref="D4:D18" si="0">IF(C4="Rejected","Critical", IF(OR(J4="Yes", AND(NOT(ISNUMBER(SEARCH("Yes",V4))),I4="Yes",ISNUMBER(SEARCH("Yes",Q4)),COUNTIF(K4:P4,"Yes")&gt;=2)), "Critical", IF(AND(NOT(ISNUMBER(SEARCH("Yes",V4))),ISNUMBER(SEARCH("Yes",Q4)), OR(I4="Yes",COUNTIF(K4:P4,"Yes")&gt;=2)), "High", IF(OR(AND(I4="Yes",ISNUMBER(SEARCH("Yes",V4))), AND(COUNTIF(K4:P4,"Yes")=1,ISNUMBER(SEARCH("Yes",Q4)),NOT(ISNUMBER(SEARCH("Yes",V4)))), AND(I4="Yes",NOT(ISNUMBER(SEARCH("Yes",Q4))))), "Moderate", IF(AND(COUNTIF(K4:P4,"Yes")=0,I4&lt;&gt;"Yes",H4&lt;&gt;"Yes", OR(G4="Yes",NOT(ISNUMBER(SEARCH("Yes",Q4))),ISNUMBER(SEARCH("Yes",V4)))), "Low", "Moderate")))))</f>
@@ -10360,13 +10363,13 @@
         <v>282</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="T4" s="2" t="s">
         <v>282</v>
@@ -10375,7 +10378,7 @@
         <v>282</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -10388,7 +10391,7 @@
         <v>Claude AI</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="D5" s="2" t="str">
         <f t="shared" si="0"/>
@@ -10432,16 +10435,16 @@
         <v>292</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="T5" s="2" t="s">
         <v>282</v>
@@ -10450,7 +10453,7 @@
         <v>282</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
     </row>
     <row r="6" spans="1:22" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -10470,7 +10473,7 @@
         <v>Moderate</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>27</v>
@@ -10507,16 +10510,16 @@
         <v>292</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="T6" s="2" t="s">
         <v>282</v>
@@ -10525,7 +10528,7 @@
         <v>282</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="7" spans="1:22" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -10538,14 +10541,14 @@
         <v>Synthesia</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="D7" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Moderate</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>27</v>
@@ -10582,16 +10585,16 @@
         <v>292</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="T7" s="2" t="s">
         <v>282</v>
@@ -10600,7 +10603,7 @@
         <v>282</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -10613,14 +10616,14 @@
         <v>Levy AI</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="D8" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Critical</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>16</v>
@@ -10654,28 +10657,28 @@
         <v>282</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>292</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -10685,17 +10688,17 @@
       </c>
       <c r="B9" s="2" t="str">
         <f>INDEX('AI Inventory'!$C$5:$C$11,6)</f>
-        <v>Pictory.AI</v>
+        <v>Startreck.AI</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="D9" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Moderate</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>27</v>
@@ -10732,16 +10735,16 @@
         <v>292</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="T9" s="2" t="s">
         <v>282</v>
@@ -10750,7 +10753,7 @@
         <v>282</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -10760,17 +10763,17 @@
       </c>
       <c r="B10" s="2" t="str">
         <f>INDEX('AI Inventory'!$C$5:$C$11,7)</f>
-        <v>Inside Hazard Navigator</v>
+        <v>Potential Hazard Navigator</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="D10" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Moderate</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>27</v>
@@ -10807,22 +10810,22 @@
         <v>292</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="V10" s="2" t="s">
         <v>292</v>
@@ -11838,7 +11841,7 @@
     </row>
     <row r="179" spans="4:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D179" s="2" t="str">
-        <f t="shared" ref="D179:D210" si="10">IF(C179="Rejected","Critical", IF(OR(J179="Yes", AND(NOT(ISNUMBER(SEARCH("Yes",V179))),I179="Yes",ISNUMBER(SEARCH("Yes",Q179)), COUNTIF(K179:P179,"Yes")&gt;=2)), "Critical", IF(AND(NOT(ISNUMBER(SEARCH("Yes",V179))),ISNUMBER(SEARCH("Yes",Q179)), OR(I179="Yes",COUNTIF(K179:P179,"Yes")&gt;=2)), "High", IF(OR(AND(I179="Yes",ISNUMBER(SEARCH("Yes",V179))), AND(COUNTIF(K179:P179,"Yes")=1,ISNUMBER(SEARCH("Yes",Q179)),NOT(ISNUMBER(SEARCH("Yes",V179)))), AND(I179="Yes",NOT(ISNUMBER(SEARCH("Yes",Q179))))), "Moderate", IF(AND(COUNTIF(K179:P179,"Yes")=0,I179&lt;&gt;"Yes", OR(G179="Yes",NOT(ISNUMBER(SEARCH("Yes",Q179))),ISNUMBER(SEARCH("Yes",V179)))), "Low", "Moderate")))))</f>
+        <f t="shared" ref="D179:D200" si="10">IF(C179="Rejected","Critical", IF(OR(J179="Yes", AND(NOT(ISNUMBER(SEARCH("Yes",V179))),I179="Yes",ISNUMBER(SEARCH("Yes",Q179)), COUNTIF(K179:P179,"Yes")&gt;=2)), "Critical", IF(AND(NOT(ISNUMBER(SEARCH("Yes",V179))),ISNUMBER(SEARCH("Yes",Q179)), OR(I179="Yes",COUNTIF(K179:P179,"Yes")&gt;=2)), "High", IF(OR(AND(I179="Yes",ISNUMBER(SEARCH("Yes",V179))), AND(COUNTIF(K179:P179,"Yes")=1,ISNUMBER(SEARCH("Yes",Q179)),NOT(ISNUMBER(SEARCH("Yes",V179)))), AND(I179="Yes",NOT(ISNUMBER(SEARCH("Yes",Q179))))), "Moderate", IF(AND(COUNTIF(K179:P179,"Yes")=0,I179&lt;&gt;"Yes", OR(G179="Yes",NOT(ISNUMBER(SEARCH("Yes",Q179))),ISNUMBER(SEARCH("Yes",V179)))), "Low", "Moderate")))))</f>
         <v>Low</v>
       </c>
     </row>
@@ -12012,8 +12015,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
-        <v>438</v>
+      <c r="A1" s="9" t="s">
+        <v>431</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -12032,8 +12035,8 @@
       <c r="P1" s="10"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A2" s="9" t="s">
-        <v>439</v>
+      <c r="A2" s="12" t="s">
+        <v>432</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -12056,46 +12059,46 @@
         <v>255</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>257</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>445</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>452</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>274</v>
@@ -12122,37 +12125,37 @@
         <v>Low</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="P4" s="2" t="s">
         <v>453</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -12179,34 +12182,34 @@
         <v>292</v>
       </c>
       <c r="G5" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="K5" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="M5" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="N5" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="J5" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>463</v>
-      </c>
       <c r="O5" s="2" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -12216,7 +12219,7 @@
       </c>
       <c r="B6" s="2" t="str">
         <f>'AI Inventory'!B7</f>
-        <v>CustomGPT.ai</v>
+        <v>SomeGPT.ai</v>
       </c>
       <c r="C6" s="2" t="str">
         <f>'AI Inventory'!C7</f>
@@ -12236,13 +12239,13 @@
         <v>292</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>282</v>
@@ -12257,10 +12260,10 @@
         <v>292</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -12284,19 +12287,19 @@
         <v>Low</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>282</v>
@@ -12305,16 +12308,16 @@
         <v>282</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>292</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -12331,44 +12334,44 @@
         <v>Levy AI</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="E8" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Moderate</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>292</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="32" customHeight="1" x14ac:dyDescent="0.2">
@@ -12378,11 +12381,11 @@
       </c>
       <c r="B9" s="2" t="str">
         <f>'AI Inventory'!B10</f>
-        <v>Pictory.AI</v>
+        <v>Startreck.AI</v>
       </c>
       <c r="C9" s="2" t="str">
         <f>'AI Inventory'!C10</f>
-        <v>Pictory.AI</v>
+        <v>Startreck.AI</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>230</v>
@@ -12392,37 +12395,37 @@
         <v>Critical</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>292</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -12436,7 +12439,7 @@
       </c>
       <c r="C10" s="2" t="str">
         <f>'AI Inventory'!C11</f>
-        <v>Inside Hazard Navigator</v>
+        <v>Potential Hazard Navigator</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>226</v>
@@ -12473,10 +12476,10 @@
         <v>292</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -13591,7 +13594,7 @@
     </row>
     <row r="196" spans="5:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E196" s="2" t="str">
-        <f t="shared" ref="E196:E227" si="6">IF(D196="Rejected","Critical", IF(NOT(OR(D196="Approved",D196="Approved with Conditions")),"Moderate", IF(COUNTIF(F196:O196,"Yes*")/COUNTA(F196:O196)&gt;=0.8,"Low", IF(COUNTIF(F196:O196,"Yes*")/COUNTA(F196:O196)&gt;=0.5,"Moderate","High"))))</f>
+        <f t="shared" ref="E196:E200" si="6">IF(D196="Rejected","Critical", IF(NOT(OR(D196="Approved",D196="Approved with Conditions")),"Moderate", IF(COUNTIF(F196:O196,"Yes*")/COUNTA(F196:O196)&gt;=0.8,"Low", IF(COUNTIF(F196:O196,"Yes*")/COUNTA(F196:O196)&gt;=0.5,"Moderate","High"))))</f>
         <v>Moderate</v>
       </c>
     </row>
@@ -13651,8 +13654,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
-        <v>470</v>
+      <c r="A1" s="9" t="s">
+        <v>463</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -13667,8 +13670,8 @@
       <c r="L1" s="10"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="9" t="s">
-        <v>471</v>
+      <c r="A2" s="12" t="s">
+        <v>464</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -13690,31 +13693,31 @@
         <v>257</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>473</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>480</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>274</v>
@@ -13730,7 +13733,7 @@
         <v>Copilot</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="D4" s="2" t="str">
         <f t="shared" ref="D4:D35" si="0">IF(C4="Rejected","Critical", IF(AND(E4="No",I4="No"),"Critical", IF(J4="No","Critical", IF(OR( C4="Not Started", I4="No", COUNTIF(E4:G4,"No")&gt;=1 ),"High", IF(H4="No","Moderate", IF(OR(J4="To Confirm", I4="To Confirm"),"Moderate", IF(COUNTIF(E4:J4,"To Confirm")=1,"Low", IF(AND(COUNTIF(E4:J4,"Yes")=COUNTA(E4:J4)-COUNTIF(E4:J4,"N/A"),COUNTA(E4:J4)-COUNTIF(E4:J4,"N/A")&gt;0),"Low", IF(COUNTA(E4:J4)-COUNTIF(E4:J4,"N/A")=0,"Low", IF(COUNTIF(E4:J4,"Yes")/(COUNTA(E4:J4)-COUNTIF(E4:J4,"N/A"))&gt;=0.5,"Moderate", "High"))))))))))</f>
@@ -13767,29 +13770,29 @@
         <v>Claude AI</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="D5" s="2" t="str">
         <f t="shared" si="0"/>
         <v>High</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
@@ -13811,22 +13814,22 @@
         <v>Moderate</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
@@ -13848,22 +13851,22 @@
         <v>Moderate</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
@@ -13878,29 +13881,29 @@
         <v>Levy AI</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="D8" s="2" t="str">
         <f t="shared" si="0"/>
         <v>High</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
@@ -13912,7 +13915,7 @@
       </c>
       <c r="B9" s="2" t="str">
         <f>'AI Inventory'!C10</f>
-        <v>Pictory.AI</v>
+        <v>Startreck.AI</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>230</v>
@@ -13922,22 +13925,22 @@
         <v>Critical</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
@@ -13949,7 +13952,7 @@
       </c>
       <c r="B10" s="2" t="str">
         <f>'AI Inventory'!C11</f>
-        <v>Inside Hazard Navigator</v>
+        <v>Potential Hazard Navigator</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>229</v>
@@ -13974,13 +13977,13 @@
         <v>282</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -16391,7 +16394,7 @@
     <row r="196" spans="3:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C196" s="2"/>
       <c r="D196" s="2" t="str">
-        <f t="shared" ref="D196:D227" si="6">IF(C196="Rejected","Critical", IF(AND(E196="No",I196="No"),"Critical", IF(J196="No","Critical", IF(OR( C196="Not Started", I196="No", COUNTIF(E196:G196,"No")&gt;=1 ),"High", IF(H196="No","Moderate", IF(OR(J196="To Confirm", I196="To Confirm"),"Moderate", IF(COUNTIF(E196:J196,"To Confirm")=1,"Low", IF(AND(COUNTIF(E196:J196,"Yes")=COUNTA(E196:J196)-COUNTIF(E196:J196,"N/A"),COUNTA(E196:J196)-COUNTIF(E196:J196,"N/A")&gt;0),"Low", IF(COUNTA(E196:J196)-COUNTIF(E196:J196,"N/A")=0,"Low", IF(COUNTIF(E196:J196,"Yes")/(COUNTA(E196:J196)-COUNTIF(E196:J196,"N/A"))&gt;=0.5,"Moderate", "High"))))))))))</f>
+        <f t="shared" ref="D196:D200" si="6">IF(C196="Rejected","Critical", IF(AND(E196="No",I196="No"),"Critical", IF(J196="No","Critical", IF(OR( C196="Not Started", I196="No", COUNTIF(E196:G196,"No")&gt;=1 ),"High", IF(H196="No","Moderate", IF(OR(J196="To Confirm", I196="To Confirm"),"Moderate", IF(COUNTIF(E196:J196,"To Confirm")=1,"Low", IF(AND(COUNTIF(E196:J196,"Yes")=COUNTA(E196:J196)-COUNTIF(E196:J196,"N/A"),COUNTA(E196:J196)-COUNTIF(E196:J196,"N/A")&gt;0),"Low", IF(COUNTA(E196:J196)-COUNTIF(E196:J196,"N/A")=0,"Low", IF(COUNTIF(E196:J196,"Yes")/(COUNTA(E196:J196)-COUNTIF(E196:J196,"N/A"))&gt;=0.5,"Moderate", "High"))))))))))</f>
         <v>Low</v>
       </c>
       <c r="E196" s="2"/>
